--- a/Formatos a Importar/Formato.xlsx
+++ b/Formatos a Importar/Formato.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB8C767-D0D3-4EAC-9A59-2182699334AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10425"/>
+    <workbookView xWindow="-15120" yWindow="3045" windowWidth="15240" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -12,6 +13,11 @@
     <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="122211"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -147,9 +153,6 @@
     <t>Nombre del Banco origen</t>
   </si>
   <si>
-    <t>Tiene empleados? 0,1</t>
-  </si>
-  <si>
     <t>campos_nombre</t>
   </si>
   <si>
@@ -181,12 +184,15 @@
   </si>
   <si>
     <t>Identificador 2</t>
+  </si>
+  <si>
+    <t>Tiene empleados? 0,1; 2 Si es de multiples transacciones</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -456,22 +462,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:D59" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A1:D59"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A1:D59" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A1:D59" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
-    <tableColumn id="4" name="Linea" dataDxfId="3"/>
-    <tableColumn id="1" name="Campo" dataDxfId="2"/>
-    <tableColumn id="2" name="Descripción" dataDxfId="1"/>
-    <tableColumn id="3" name="Tabla" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Linea" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Campo" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descripción" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Tabla" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -509,7 +515,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -581,7 +587,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -754,13 +760,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="24.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="44.7109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9.140625" style="2"/>
   </cols>
@@ -790,7 +796,7 @@
         <v>41</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -798,13 +804,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>53</v>
-      </c>
       <c r="D3" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -815,10 +821,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -826,13 +832,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="23" t="s">
         <v>39</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -843,10 +849,10 @@
         <v>6</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -854,13 +860,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>42</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -868,13 +874,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>51</v>
-      </c>
       <c r="D8" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -888,7 +894,7 @@
         <v>24</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -902,7 +908,7 @@
         <v>25</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -916,7 +922,7 @@
         <v>26</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -930,7 +936,7 @@
         <v>27</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -944,7 +950,7 @@
         <v>28</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -958,7 +964,7 @@
         <v>29</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -972,7 +978,7 @@
         <v>30</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -986,7 +992,7 @@
         <v>31</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1000,7 +1006,7 @@
         <v>32</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1014,7 +1020,7 @@
         <v>33</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1028,7 +1034,7 @@
         <v>34</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1042,7 +1048,7 @@
         <v>35</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -1056,7 +1062,7 @@
         <v>36</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1070,7 +1076,7 @@
         <v>37</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1084,7 +1090,7 @@
         <v>38</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1098,7 +1104,7 @@
         <v>39</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1112,7 +1118,7 @@
         <v>40</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1126,7 +1132,7 @@
         <v>24</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1140,7 +1146,7 @@
         <v>25</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1154,7 +1160,7 @@
         <v>26</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1168,7 +1174,7 @@
         <v>27</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1182,7 +1188,7 @@
         <v>28</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1196,7 +1202,7 @@
         <v>29</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1210,7 +1216,7 @@
         <v>30</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1224,7 +1230,7 @@
         <v>31</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1238,7 +1244,7 @@
         <v>32</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1252,7 +1258,7 @@
         <v>33</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1266,7 +1272,7 @@
         <v>34</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1280,7 +1286,7 @@
         <v>35</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1294,7 +1300,7 @@
         <v>36</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1308,7 +1314,7 @@
         <v>37</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1322,7 +1328,7 @@
         <v>38</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1336,7 +1342,7 @@
         <v>39</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1350,7 +1356,7 @@
         <v>40</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1364,7 +1370,7 @@
         <v>24</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1378,7 +1384,7 @@
         <v>25</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
@@ -1392,10 +1398,10 @@
         <v>26</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="27">
         <v>45</v>
       </c>
@@ -1406,7 +1412,7 @@
         <v>27</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1420,10 +1426,10 @@
         <v>28</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="27">
         <v>47</v>
       </c>
@@ -1434,10 +1440,10 @@
         <v>29</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="24">
         <v>48</v>
       </c>
@@ -1448,10 +1454,10 @@
         <v>30</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="27">
         <v>49</v>
       </c>
@@ -1462,7 +1468,7 @@
         <v>31</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1476,10 +1482,10 @@
         <v>32</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="27">
         <v>51</v>
       </c>
@@ -1490,10 +1496,10 @@
         <v>33</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="24">
         <v>52</v>
       </c>
@@ -1504,10 +1510,10 @@
         <v>34</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="27">
         <v>53</v>
       </c>
@@ -1518,10 +1524,10 @@
         <v>35</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="24">
         <v>54</v>
       </c>
@@ -1532,10 +1538,10 @@
         <v>36</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="27">
         <v>55</v>
       </c>
@@ -1546,10 +1552,10 @@
         <v>37</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="24">
         <v>56</v>
       </c>
@@ -1560,10 +1566,10 @@
         <v>38</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="15.6" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="27">
         <v>57</v>
       </c>
@@ -1574,7 +1580,7 @@
         <v>39</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -1588,7 +1594,7 @@
         <v>40</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1601,7 +1607,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -1610,7 +1616,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
